--- a/artfynd/A 56071-2024 artfynd.xlsx
+++ b/artfynd/A 56071-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428944</v>
       </c>
       <c r="B2" t="n">
-        <v>110520</v>
+        <v>110527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>123428943</v>
       </c>
       <c r="B3" t="n">
-        <v>110520</v>
+        <v>110527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56071-2024 artfynd.xlsx
+++ b/artfynd/A 56071-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428943</v>
+        <v>123428944</v>
       </c>
       <c r="B2" t="n">
-        <v>110530</v>
+        <v>110547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384639</v>
+        <v>384655</v>
       </c>
       <c r="R2" t="n">
-        <v>6585851</v>
+        <v>6585847</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428944</v>
+        <v>123428943</v>
       </c>
       <c r="B3" t="n">
-        <v>110530</v>
+        <v>110547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384655</v>
+        <v>384639</v>
       </c>
       <c r="R3" t="n">
-        <v>6585847</v>
+        <v>6585851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 56071-2024 artfynd.xlsx
+++ b/artfynd/A 56071-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428944</v>
       </c>
       <c r="B2" t="n">
-        <v>110547</v>
+        <v>110569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>123428943</v>
       </c>
       <c r="B3" t="n">
-        <v>110547</v>
+        <v>110569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56071-2024 artfynd.xlsx
+++ b/artfynd/A 56071-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428944</v>
       </c>
       <c r="B2" t="n">
-        <v>110569</v>
+        <v>110571</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>123428943</v>
       </c>
       <c r="B3" t="n">
-        <v>110569</v>
+        <v>110571</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56071-2024 artfynd.xlsx
+++ b/artfynd/A 56071-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428944</v>
       </c>
       <c r="B2" t="n">
-        <v>110571</v>
+        <v>110146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>123428943</v>
       </c>
       <c r="B3" t="n">
-        <v>110571</v>
+        <v>110146</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56071-2024 artfynd.xlsx
+++ b/artfynd/A 56071-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428944</v>
+        <v>123428943</v>
       </c>
       <c r="B2" t="n">
-        <v>110146</v>
+        <v>110149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384655</v>
+        <v>384639</v>
       </c>
       <c r="R2" t="n">
-        <v>6585847</v>
+        <v>6585851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428943</v>
+        <v>123428944</v>
       </c>
       <c r="B3" t="n">
-        <v>110146</v>
+        <v>110149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384639</v>
+        <v>384655</v>
       </c>
       <c r="R3" t="n">
-        <v>6585851</v>
+        <v>6585847</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 56071-2024 artfynd.xlsx
+++ b/artfynd/A 56071-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428943</v>
+        <v>123428944</v>
       </c>
       <c r="B2" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384639</v>
+        <v>384655</v>
       </c>
       <c r="R2" t="n">
-        <v>6585851</v>
+        <v>6585847</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428944</v>
+        <v>123428943</v>
       </c>
       <c r="B3" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384655</v>
+        <v>384639</v>
       </c>
       <c r="R3" t="n">
-        <v>6585847</v>
+        <v>6585851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
